--- a/flow/20231121_calendar_readings/data.xlsx
+++ b/flow/20231121_calendar_readings/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26924"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\GitHub\prayer-service-scripts\flow\20231121_calendar_readings\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andri\Documents\GitHub\prayer-service-scripts\flow\20231121_calendar_readings\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EDA417E-15A5-430F-81E8-999BD73202A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{159E2030-57BB-41ED-BDF2-408472C61BED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="-5925" yWindow="6495" windowWidth="24705" windowHeight="11820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Аркуш2" sheetId="2" r:id="rId1"/>
@@ -2290,7 +2290,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2304,27 +2304,15 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Звичайний" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF7030A0"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2604,7 +2592,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97F94514-8FE2-4F45-B64E-AB9562BC5B2E}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:D367"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2613,20 +2600,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>718</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>719</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="6" t="s">
         <v>720</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="6" t="s">
         <v>721</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2640,7 +2627,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2654,7 +2641,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1</v>
       </c>
@@ -2668,7 +2655,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1</v>
       </c>
@@ -2682,7 +2669,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>1</v>
       </c>
@@ -2696,7 +2683,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>1</v>
       </c>
@@ -2710,7 +2697,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>1</v>
       </c>
@@ -2724,147 +2711,147 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>1</v>
       </c>
       <c r="B9">
         <v>8</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="1" t="s">
         <v>395</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="10" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>1</v>
       </c>
       <c r="B10">
         <v>9</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>1</v>
       </c>
       <c r="B11">
         <v>10</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>1</v>
       </c>
       <c r="B12">
         <v>11</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>1</v>
       </c>
       <c r="B13">
         <v>12</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>1</v>
       </c>
       <c r="B14">
         <v>13</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="1" t="s">
         <v>398</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" ht="75" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>1</v>
       </c>
       <c r="B15">
         <v>14</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="1" t="s">
         <v>399</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>1</v>
       </c>
       <c r="B16">
         <v>15</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="1" t="s">
         <v>401</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>1</v>
       </c>
       <c r="B17">
         <v>16</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="1" t="s">
         <v>402</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>1</v>
       </c>
       <c r="B18">
         <v>17</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="1" t="s">
         <v>715</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>1</v>
       </c>
@@ -2878,7 +2865,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>1</v>
       </c>
@@ -2892,7 +2879,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>1</v>
       </c>
@@ -2906,7 +2893,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>1</v>
       </c>
@@ -2920,7 +2907,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>1</v>
       </c>
@@ -2934,7 +2921,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>1</v>
       </c>
@@ -2948,7 +2935,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="25" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>1</v>
       </c>
@@ -2962,7 +2949,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>1</v>
       </c>
@@ -2976,7 +2963,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>1</v>
       </c>
@@ -2990,7 +2977,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>1</v>
       </c>
@@ -3005,7 +2992,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>1</v>
       </c>
@@ -3019,7 +3006,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>1</v>
       </c>
@@ -3033,7 +3020,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>1</v>
       </c>
@@ -3075,7 +3062,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>2</v>
       </c>
@@ -3103,7 +3090,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>2</v>
       </c>
@@ -3131,7 +3118,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>2</v>
       </c>
@@ -3145,7 +3132,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>2</v>
       </c>
@@ -3187,7 +3174,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="42" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>2</v>
       </c>
@@ -3201,7 +3188,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>2</v>
       </c>
@@ -3215,7 +3202,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>2</v>
       </c>
@@ -3229,7 +3216,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>2</v>
       </c>
@@ -3243,7 +3230,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>2</v>
       </c>
@@ -3257,7 +3244,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="47" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>2</v>
       </c>
@@ -3271,7 +3258,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>2</v>
       </c>
@@ -3285,7 +3272,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="49" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>2</v>
       </c>
@@ -3299,7 +3286,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>2</v>
       </c>
@@ -3313,7 +3300,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="51" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>2</v>
       </c>
@@ -3327,7 +3314,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="52" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>2</v>
       </c>
@@ -3341,7 +3328,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>2</v>
       </c>
@@ -3355,7 +3342,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>2</v>
       </c>
@@ -3369,7 +3356,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="55" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>2</v>
       </c>
@@ -3383,7 +3370,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>2</v>
       </c>
@@ -3397,7 +3384,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="57" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>2</v>
       </c>
@@ -3411,7 +3398,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="58" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>2</v>
       </c>
@@ -3425,7 +3412,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="59" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>2</v>
       </c>
@@ -3439,7 +3426,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="60" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>2</v>
       </c>
@@ -3453,7 +3440,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="61" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>2</v>
       </c>
@@ -3467,7 +3454,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="62" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>3</v>
       </c>
@@ -3481,7 +3468,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="63" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>3</v>
       </c>
@@ -3495,7 +3482,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="64" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>3</v>
       </c>
@@ -3509,7 +3496,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="65" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>3</v>
       </c>
@@ -3523,7 +3510,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="66" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>3</v>
       </c>
@@ -3537,7 +3524,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="67" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>3</v>
       </c>
@@ -3551,7 +3538,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="68" spans="1:4" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>3</v>
       </c>
@@ -3565,7 +3552,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="69" spans="1:4" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>3</v>
       </c>
@@ -3579,7 +3566,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="70" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>3</v>
       </c>
@@ -3593,7 +3580,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="71" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>3</v>
       </c>
@@ -3607,7 +3594,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="72" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>3</v>
       </c>
@@ -3621,7 +3608,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="73" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>3</v>
       </c>
@@ -3635,7 +3622,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="74" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>3</v>
       </c>
@@ -3649,7 +3636,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="75" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>3</v>
       </c>
@@ -3663,7 +3650,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="76" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>3</v>
       </c>
@@ -3677,7 +3664,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="77" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>3</v>
       </c>
@@ -3691,7 +3678,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="78" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>3</v>
       </c>
@@ -3705,7 +3692,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="79" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>3</v>
       </c>
@@ -3719,7 +3706,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="80" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>3</v>
       </c>
@@ -3733,7 +3720,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="81" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>3</v>
       </c>
@@ -3747,7 +3734,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="82" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>3</v>
       </c>
@@ -3761,7 +3748,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="83" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>3</v>
       </c>
@@ -3775,7 +3762,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="84" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>3</v>
       </c>
@@ -3789,7 +3776,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="85" spans="1:4" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>3</v>
       </c>
@@ -3803,7 +3790,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="86" spans="1:4" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>3</v>
       </c>
@@ -3817,7 +3804,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="87" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>3</v>
       </c>
@@ -3831,7 +3818,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="88" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>3</v>
       </c>
@@ -3845,7 +3832,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="89" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>3</v>
       </c>
@@ -3859,7 +3846,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="90" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>3</v>
       </c>
@@ -3873,7 +3860,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="91" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>3</v>
       </c>
@@ -3887,7 +3874,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="92" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>3</v>
       </c>
@@ -3901,7 +3888,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="93" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>4</v>
       </c>
@@ -3915,7 +3902,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="94" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>4</v>
       </c>
@@ -3929,7 +3916,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="95" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>4</v>
       </c>
@@ -3943,7 +3930,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="96" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>4</v>
       </c>
@@ -3957,7 +3944,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="97" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>4</v>
       </c>
@@ -3971,7 +3958,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="98" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>4</v>
       </c>
@@ -3985,7 +3972,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="99" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>4</v>
       </c>
@@ -3999,7 +3986,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="100" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>4</v>
       </c>
@@ -4013,7 +4000,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="101" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>4</v>
       </c>
@@ -4027,7 +4014,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="102" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>4</v>
       </c>
@@ -4041,7 +4028,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="103" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>4</v>
       </c>
@@ -4055,7 +4042,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="104" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>4</v>
       </c>
@@ -4069,7 +4056,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="105" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>4</v>
       </c>
@@ -4083,7 +4070,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="106" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>4</v>
       </c>
@@ -4097,7 +4084,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="107" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>4</v>
       </c>
@@ -4111,7 +4098,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="108" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>4</v>
       </c>
@@ -4125,7 +4112,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="109" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>4</v>
       </c>
@@ -4139,7 +4126,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="110" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>4</v>
       </c>
@@ -4153,7 +4140,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="111" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>4</v>
       </c>
@@ -4167,7 +4154,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="112" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>4</v>
       </c>
@@ -4181,7 +4168,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="113" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>4</v>
       </c>
@@ -4195,7 +4182,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="114" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>4</v>
       </c>
@@ -4209,7 +4196,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="115" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>4</v>
       </c>
@@ -4223,7 +4210,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="116" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>4</v>
       </c>
@@ -4237,7 +4224,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="117" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>4</v>
       </c>
@@ -4252,7 +4239,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="118" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>4</v>
       </c>
@@ -4266,7 +4253,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="119" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>4</v>
       </c>
@@ -4280,7 +4267,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="120" spans="1:4" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:4" ht="75" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>4</v>
       </c>
@@ -4294,7 +4281,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="121" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>4</v>
       </c>
@@ -4308,7 +4295,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="122" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>4</v>
       </c>
@@ -4322,7 +4309,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="123" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>5</v>
       </c>
@@ -4336,7 +4323,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="124" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>5</v>
       </c>
@@ -4350,7 +4337,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="125" spans="1:4" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:4" ht="75" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>5</v>
       </c>
@@ -4364,7 +4351,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="126" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>5</v>
       </c>
@@ -4378,7 +4365,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="127" spans="1:4" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>5</v>
       </c>
@@ -4392,7 +4379,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="128" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>5</v>
       </c>
@@ -4406,7 +4393,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="129" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>5</v>
       </c>
@@ -4420,7 +4407,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="130" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>5</v>
       </c>
@@ -4434,7 +4421,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="131" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>5</v>
       </c>
@@ -4448,7 +4435,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="132" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>5</v>
       </c>
@@ -4462,7 +4449,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="133" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>5</v>
       </c>
@@ -4476,7 +4463,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="134" spans="1:4" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>5</v>
       </c>
@@ -4490,7 +4477,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="135" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>5</v>
       </c>
@@ -4504,7 +4491,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="136" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>5</v>
       </c>
@@ -4518,7 +4505,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="137" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>5</v>
       </c>
@@ -4532,7 +4519,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="138" spans="1:4" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>5</v>
       </c>
@@ -4546,7 +4533,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="139" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>5</v>
       </c>
@@ -4560,7 +4547,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="140" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>5</v>
       </c>
@@ -4574,7 +4561,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="141" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>5</v>
       </c>
@@ -4588,7 +4575,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="142" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>5</v>
       </c>
@@ -4602,7 +4589,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="143" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>5</v>
       </c>
@@ -4617,7 +4604,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="144" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>5</v>
       </c>
@@ -4631,7 +4618,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="145" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>5</v>
       </c>
@@ -4645,7 +4632,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="146" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>5</v>
       </c>
@@ -4659,7 +4646,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="147" spans="1:4" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>5</v>
       </c>
@@ -4673,7 +4660,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="148" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>5</v>
       </c>
@@ -4687,7 +4674,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="149" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>5</v>
       </c>
@@ -4701,7 +4688,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="150" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>5</v>
       </c>
@@ -4715,7 +4702,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="151" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>5</v>
       </c>
@@ -4729,7 +4716,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="152" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>5</v>
       </c>
@@ -4743,7 +4730,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="153" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>5</v>
       </c>
@@ -4757,7 +4744,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="154" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>6</v>
       </c>
@@ -4771,7 +4758,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="155" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>6</v>
       </c>
@@ -4785,7 +4772,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="156" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>6</v>
       </c>
@@ -4799,7 +4786,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="157" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>6</v>
       </c>
@@ -4813,7 +4800,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="158" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>6</v>
       </c>
@@ -4827,7 +4814,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="159" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>6</v>
       </c>
@@ -4841,7 +4828,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="160" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>6</v>
       </c>
@@ -4855,7 +4842,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="161" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>6</v>
       </c>
@@ -4869,7 +4856,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="162" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>6</v>
       </c>
@@ -4883,7 +4870,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="163" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>6</v>
       </c>
@@ -4897,7 +4884,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="164" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>6</v>
       </c>
@@ -4912,7 +4899,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="165" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>6</v>
       </c>
@@ -4926,7 +4913,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="166" spans="1:4" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>6</v>
       </c>
@@ -4940,7 +4927,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="167" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>6</v>
       </c>
@@ -4954,7 +4941,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="168" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>6</v>
       </c>
@@ -4968,7 +4955,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="169" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>6</v>
       </c>
@@ -4982,7 +4969,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="170" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>6</v>
       </c>
@@ -4996,7 +4983,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="171" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>6</v>
       </c>
@@ -5010,7 +4997,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="172" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>6</v>
       </c>
@@ -5024,7 +5011,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="173" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>6</v>
       </c>
@@ -5038,7 +5025,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="174" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>6</v>
       </c>
@@ -5052,7 +5039,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="175" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>6</v>
       </c>
@@ -5066,7 +5053,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="176" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>6</v>
       </c>
@@ -5080,7 +5067,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="177" spans="1:4" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>6</v>
       </c>
@@ -5094,7 +5081,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="178" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>6</v>
       </c>
@@ -5108,7 +5095,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="179" spans="1:4" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>6</v>
       </c>
@@ -5122,7 +5109,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="180" spans="1:4" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>6</v>
       </c>
@@ -5136,7 +5123,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="181" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>6</v>
       </c>
@@ -5150,7 +5137,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="182" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>6</v>
       </c>
@@ -5164,7 +5151,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="183" spans="1:4" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>6</v>
       </c>
@@ -5178,7 +5165,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="184" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>7</v>
       </c>
@@ -5192,7 +5179,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="185" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>7</v>
       </c>
@@ -5207,7 +5194,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="186" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>7</v>
       </c>
@@ -5221,7 +5208,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="187" spans="1:4" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:4" ht="75" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>7</v>
       </c>
@@ -5235,7 +5222,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="188" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>7</v>
       </c>
@@ -5250,7 +5237,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="189" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>7</v>
       </c>
@@ -5264,7 +5251,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="190" spans="1:4" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>7</v>
       </c>
@@ -5278,7 +5265,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="191" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>7</v>
       </c>
@@ -5292,7 +5279,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="192" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>7</v>
       </c>
@@ -5306,7 +5293,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="193" spans="1:4" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:4" ht="75" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>7</v>
       </c>
@@ -5320,7 +5307,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="194" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>7</v>
       </c>
@@ -5334,7 +5321,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="195" spans="1:4" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>7</v>
       </c>
@@ -5348,7 +5335,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="196" spans="1:4" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>7</v>
       </c>
@@ -5362,7 +5349,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="197" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>7</v>
       </c>
@@ -5376,7 +5363,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="198" spans="1:4" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>7</v>
       </c>
@@ -5390,7 +5377,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="199" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>7</v>
       </c>
@@ -5404,7 +5391,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="200" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>7</v>
       </c>
@@ -5418,7 +5405,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="201" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>7</v>
       </c>
@@ -5432,7 +5419,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="202" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>7</v>
       </c>
@@ -5446,7 +5433,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="203" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>7</v>
       </c>
@@ -5460,7 +5447,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="204" spans="1:4" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:4" ht="75" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>7</v>
       </c>
@@ -5474,7 +5461,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="205" spans="1:4" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>7</v>
       </c>
@@ -5488,7 +5475,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="206" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>7</v>
       </c>
@@ -5502,7 +5489,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="207" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>7</v>
       </c>
@@ -5516,7 +5503,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="208" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A208">
         <v>7</v>
       </c>
@@ -5530,7 +5517,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="209" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>7</v>
       </c>
@@ -5544,7 +5531,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="210" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A210">
         <v>7</v>
       </c>
@@ -5558,7 +5545,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="211" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>7</v>
       </c>
@@ -5572,7 +5559,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="212" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A212">
         <v>7</v>
       </c>
@@ -5586,7 +5573,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="213" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A213">
         <v>7</v>
       </c>
@@ -5600,7 +5587,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="214" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>7</v>
       </c>
@@ -5614,7 +5601,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="215" spans="1:4" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:4" ht="75" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>8</v>
       </c>
@@ -5628,7 +5615,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="216" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A216">
         <v>8</v>
       </c>
@@ -5642,7 +5629,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="217" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>8</v>
       </c>
@@ -5656,7 +5643,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="218" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A218">
         <v>8</v>
       </c>
@@ -5670,7 +5657,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="219" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>8</v>
       </c>
@@ -5684,7 +5671,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="220" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A220">
         <v>8</v>
       </c>
@@ -5698,7 +5685,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="221" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A221">
         <v>8</v>
       </c>
@@ -5712,7 +5699,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="222" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A222">
         <v>8</v>
       </c>
@@ -5726,7 +5713,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="223" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A223">
         <v>8</v>
       </c>
@@ -5741,7 +5728,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="224" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A224">
         <v>8</v>
       </c>
@@ -5755,7 +5742,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="225" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A225">
         <v>8</v>
       </c>
@@ -5769,7 +5756,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="226" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A226">
         <v>8</v>
       </c>
@@ -5783,7 +5770,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="227" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>8</v>
       </c>
@@ -5797,7 +5784,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="228" spans="1:4" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A228">
         <v>8</v>
       </c>
@@ -5811,7 +5798,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="229" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>8</v>
       </c>
@@ -5825,7 +5812,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="230" spans="1:4" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A230">
         <v>8</v>
       </c>
@@ -5839,7 +5826,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="231" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>8</v>
       </c>
@@ -5853,7 +5840,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="232" spans="1:4" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A232">
         <v>8</v>
       </c>
@@ -5867,7 +5854,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="233" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A233">
         <v>8</v>
       </c>
@@ -5881,7 +5868,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="234" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A234">
         <v>8</v>
       </c>
@@ -5895,7 +5882,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="235" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A235">
         <v>8</v>
       </c>
@@ -5909,7 +5896,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="236" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A236">
         <v>8</v>
       </c>
@@ -5923,7 +5910,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="237" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A237">
         <v>8</v>
       </c>
@@ -5937,7 +5924,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="238" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A238">
         <v>8</v>
       </c>
@@ -5951,7 +5938,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="239" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A239">
         <v>8</v>
       </c>
@@ -5965,7 +5952,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="240" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A240">
         <v>8</v>
       </c>
@@ -5979,7 +5966,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="241" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A241">
         <v>8</v>
       </c>
@@ -5993,7 +5980,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="242" spans="1:4" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:4" ht="75" x14ac:dyDescent="0.25">
       <c r="A242">
         <v>8</v>
       </c>
@@ -6007,7 +5994,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="243" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A243">
         <v>8</v>
       </c>
@@ -6021,7 +6008,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="244" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A244">
         <v>8</v>
       </c>
@@ -6035,7 +6022,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="245" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A245">
         <v>8</v>
       </c>
@@ -6050,7 +6037,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="246" spans="1:4" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:4" ht="75" x14ac:dyDescent="0.25">
       <c r="A246">
         <v>9</v>
       </c>
@@ -6064,7 +6051,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="247" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A247">
         <v>9</v>
       </c>
@@ -6078,7 +6065,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="248" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A248">
         <v>9</v>
       </c>
@@ -6092,7 +6079,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="249" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A249">
         <v>9</v>
       </c>
@@ -6106,7 +6093,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="250" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A250">
         <v>9</v>
       </c>
@@ -6120,7 +6107,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="251" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A251">
         <v>9</v>
       </c>
@@ -6134,7 +6121,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="252" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A252">
         <v>9</v>
       </c>
@@ -6148,7 +6135,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="253" spans="1:4" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A253">
         <v>9</v>
       </c>
@@ -6162,7 +6149,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="254" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A254">
         <v>9</v>
       </c>
@@ -6176,7 +6163,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="255" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A255">
         <v>9</v>
       </c>
@@ -6190,7 +6177,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="256" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A256">
         <v>9</v>
       </c>
@@ -6204,7 +6191,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="257" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A257">
         <v>9</v>
       </c>
@@ -6218,7 +6205,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="258" spans="1:4" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A258">
         <v>9</v>
       </c>
@@ -6232,7 +6219,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="259" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A259">
         <v>9</v>
       </c>
@@ -6246,7 +6233,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="260" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A260">
         <v>9</v>
       </c>
@@ -6260,7 +6247,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="261" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A261">
         <v>9</v>
       </c>
@@ -6274,7 +6261,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="262" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A262">
         <v>9</v>
       </c>
@@ -6288,7 +6275,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="263" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A263">
         <v>9</v>
       </c>
@@ -6302,7 +6289,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="264" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A264">
         <v>9</v>
       </c>
@@ -6316,7 +6303,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="265" spans="1:4" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A265">
         <v>9</v>
       </c>
@@ -6330,7 +6317,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="266" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A266">
         <v>9</v>
       </c>
@@ -6344,7 +6331,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="267" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A267">
         <v>9</v>
       </c>
@@ -6358,7 +6345,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="268" spans="1:4" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A268">
         <v>9</v>
       </c>
@@ -6372,7 +6359,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="269" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A269">
         <v>9</v>
       </c>
@@ -6386,7 +6373,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="270" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A270">
         <v>9</v>
       </c>
@@ -6400,7 +6387,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="271" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A271">
         <v>9</v>
       </c>
@@ -6414,7 +6401,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="272" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A272">
         <v>9</v>
       </c>
@@ -6428,7 +6415,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="273" spans="1:4" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:4" ht="75" x14ac:dyDescent="0.25">
       <c r="A273">
         <v>9</v>
       </c>
@@ -6442,7 +6429,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="274" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A274">
         <v>9</v>
       </c>
@@ -6456,7 +6443,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="275" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A275">
         <v>9</v>
       </c>
@@ -6470,7 +6457,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="276" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A276">
         <v>10</v>
       </c>
@@ -6484,7 +6471,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="277" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A277">
         <v>10</v>
       </c>
@@ -6498,7 +6485,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="278" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A278">
         <v>10</v>
       </c>
@@ -6512,7 +6499,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="279" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A279">
         <v>10</v>
       </c>
@@ -6526,7 +6513,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="280" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A280">
         <v>10</v>
       </c>
@@ -6540,7 +6527,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="281" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A281">
         <v>10</v>
       </c>
@@ -6554,7 +6541,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="282" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A282">
         <v>10</v>
       </c>
@@ -6568,7 +6555,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="283" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A283">
         <v>10</v>
       </c>
@@ -6582,7 +6569,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="284" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A284">
         <v>10</v>
       </c>
@@ -6597,7 +6584,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="285" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A285">
         <v>10</v>
       </c>
@@ -6611,7 +6598,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="286" spans="1:4" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:4" ht="75" x14ac:dyDescent="0.25">
       <c r="A286">
         <v>10</v>
       </c>
@@ -6625,7 +6612,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="287" spans="1:4" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A287">
         <v>10</v>
       </c>
@@ -6639,7 +6626,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="288" spans="1:4" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A288">
         <v>10</v>
       </c>
@@ -6653,7 +6640,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="289" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A289">
         <v>10</v>
       </c>
@@ -6667,7 +6654,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="290" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A290">
         <v>10</v>
       </c>
@@ -6681,7 +6668,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="291" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A291">
         <v>10</v>
       </c>
@@ -6695,7 +6682,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="292" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A292">
         <v>10</v>
       </c>
@@ -6709,7 +6696,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="293" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A293">
         <v>10</v>
       </c>
@@ -6724,7 +6711,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="294" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A294">
         <v>10</v>
       </c>
@@ -6738,7 +6725,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="295" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A295">
         <v>10</v>
       </c>
@@ -6752,7 +6739,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="296" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A296">
         <v>10</v>
       </c>
@@ -6766,7 +6753,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="297" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A297">
         <v>10</v>
       </c>
@@ -6780,7 +6767,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="298" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A298">
         <v>10</v>
       </c>
@@ -6794,7 +6781,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="299" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A299">
         <v>10</v>
       </c>
@@ -6808,7 +6795,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="300" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A300">
         <v>10</v>
       </c>
@@ -6822,7 +6809,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="301" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A301">
         <v>10</v>
       </c>
@@ -6836,7 +6823,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="302" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A302">
         <v>10</v>
       </c>
@@ -6850,7 +6837,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="303" spans="1:4" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:4" ht="75" x14ac:dyDescent="0.25">
       <c r="A303">
         <v>10</v>
       </c>
@@ -6864,7 +6851,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="304" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A304">
         <v>10</v>
       </c>
@@ -6878,7 +6865,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="305" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A305">
         <v>10</v>
       </c>
@@ -6892,7 +6879,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="306" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A306">
         <v>10</v>
       </c>
@@ -6906,7 +6893,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="307" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A307">
         <v>11</v>
       </c>
@@ -6920,7 +6907,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="308" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A308">
         <v>11</v>
       </c>
@@ -6934,7 +6921,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="309" spans="1:4" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:4" ht="75" x14ac:dyDescent="0.25">
       <c r="A309">
         <v>11</v>
       </c>
@@ -6948,7 +6935,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="310" spans="1:4" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A310">
         <v>11</v>
       </c>
@@ -6962,7 +6949,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="311" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A311">
         <v>11</v>
       </c>
@@ -6976,7 +6963,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="312" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A312">
         <v>11</v>
       </c>
@@ -6990,7 +6977,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="313" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A313">
         <v>11</v>
       </c>
@@ -7004,7 +6991,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="314" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A314">
         <v>11</v>
       </c>
@@ -7018,7 +7005,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="315" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A315">
         <v>11</v>
       </c>
@@ -7032,7 +7019,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="316" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A316">
         <v>11</v>
       </c>
@@ -7046,7 +7033,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="317" spans="1:4" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A317">
         <v>11</v>
       </c>
@@ -7060,7 +7047,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="318" spans="1:4" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A318">
         <v>11</v>
       </c>
@@ -7074,7 +7061,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="319" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A319">
         <v>11</v>
       </c>
@@ -7088,7 +7075,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="320" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A320">
         <v>11</v>
       </c>
@@ -7103,7 +7090,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="321" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A321">
         <v>11</v>
       </c>
@@ -7117,7 +7104,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="322" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A322">
         <v>11</v>
       </c>
@@ -7132,7 +7119,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="323" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A323">
         <v>11</v>
       </c>
@@ -7146,7 +7133,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="324" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A324">
         <v>11</v>
       </c>
@@ -7160,7 +7147,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="325" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A325">
         <v>11</v>
       </c>
@@ -7174,7 +7161,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="326" spans="1:4" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:4" ht="90" x14ac:dyDescent="0.25">
       <c r="A326">
         <v>11</v>
       </c>
@@ -7188,7 +7175,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="327" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A327">
         <v>11</v>
       </c>
@@ -7202,7 +7189,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="328" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A328">
         <v>11</v>
       </c>
@@ -7216,7 +7203,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="329" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A329">
         <v>11</v>
       </c>
@@ -7230,7 +7217,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="330" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A330">
         <v>11</v>
       </c>
@@ -7244,7 +7231,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="331" spans="1:4" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A331">
         <v>11</v>
       </c>
@@ -7258,7 +7245,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="332" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A332">
         <v>11</v>
       </c>
@@ -7272,7 +7259,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="333" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A333">
         <v>11</v>
       </c>
@@ -7286,7 +7273,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="334" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A334">
         <v>11</v>
       </c>
@@ -7300,7 +7287,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="335" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A335">
         <v>11</v>
       </c>
@@ -7314,7 +7301,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="336" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A336">
         <v>11</v>
       </c>
@@ -7329,7 +7316,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="337" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A337">
         <v>12</v>
       </c>
@@ -7343,7 +7330,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="338" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A338">
         <v>12</v>
       </c>
@@ -7357,7 +7344,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="339" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A339">
         <v>12</v>
       </c>
@@ -7371,7 +7358,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="340" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A340">
         <v>12</v>
       </c>
@@ -7385,7 +7372,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="341" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A341">
         <v>12</v>
       </c>
@@ -7400,7 +7387,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="342" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A342">
         <v>12</v>
       </c>
@@ -7414,7 +7401,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="343" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A343">
         <v>12</v>
       </c>
@@ -7428,7 +7415,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="344" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A344">
         <v>12</v>
       </c>
@@ -7442,7 +7429,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="345" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A345">
         <v>12</v>
       </c>
@@ -7456,7 +7443,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="346" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A346">
         <v>12</v>
       </c>
@@ -7470,7 +7457,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="347" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A347">
         <v>12</v>
       </c>
@@ -7484,7 +7471,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="348" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A348">
         <v>12</v>
       </c>
@@ -7498,7 +7485,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="349" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A349">
         <v>12</v>
       </c>
@@ -7512,7 +7499,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="350" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A350">
         <v>12</v>
       </c>
@@ -7526,7 +7513,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="351" spans="1:4" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A351">
         <v>12</v>
       </c>
@@ -7540,7 +7527,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="352" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A352">
         <v>12</v>
       </c>
@@ -7554,7 +7541,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="353" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A353">
         <v>12</v>
       </c>
@@ -7568,7 +7555,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="354" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A354">
         <v>12</v>
       </c>
@@ -7582,7 +7569,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="355" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A355">
         <v>12</v>
       </c>
@@ -7596,7 +7583,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="356" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A356">
         <v>12</v>
       </c>
@@ -7610,7 +7597,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="357" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A357">
         <v>12</v>
       </c>
@@ -7624,7 +7611,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="358" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A358">
         <v>12</v>
       </c>
@@ -7638,7 +7625,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="359" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A359">
         <v>12</v>
       </c>
@@ -7652,7 +7639,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="360" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A360">
         <v>12</v>
       </c>
@@ -7666,7 +7653,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="361" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A361">
         <v>12</v>
       </c>
@@ -7680,7 +7667,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="362" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A362">
         <v>12</v>
       </c>
@@ -7708,7 +7695,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="364" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A364">
         <v>12</v>
       </c>
@@ -7722,7 +7709,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="365" spans="1:4" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:4" ht="90" x14ac:dyDescent="0.25">
       <c r="A365">
         <v>12</v>
       </c>
@@ -7736,7 +7723,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="366" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A366">
         <v>12</v>
       </c>
@@ -7750,7 +7737,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="367" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A367">
         <v>12</v>
       </c>
@@ -7765,11 +7752,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D367" xr:uid="{97F94514-8FE2-4F45-B64E-AB9562BC5B2E}">
-    <filterColumn colId="2">
-      <colorFilter dxfId="0"/>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:D367" xr:uid="{97F94514-8FE2-4F45-B64E-AB9562BC5B2E}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
